--- a/基本設計/17_トランザクションと排他_基本設計書.xlsx
+++ b/基本設計/17_トランザクションと排他_基本設計書.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R6defde851351446c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rc0c64b0ef5904383"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="29_トランザクション" sheetId="30" r:id="Radc6e99a9a074418"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30_排他・論理削除" sheetId="31" r:id="R66b8bc96bd2a4688"/>
-  </x:sheets>
-</x:workbook>
+<ns0:workbook xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <ns0:sheets>
+    <ns0:sheet name="00_表紙" sheetId="1" ns1:id="R4a212c9c352c42cf"/>
+    <ns0:sheet name="01_改訂履歴" sheetId="2" ns1:id="Rae7b41d351854af2"/>
+    <ns0:sheet name="29_トランザクション" sheetId="30" ns1:id="Rdc4d4f4d2c8045f1"/>
+    <ns0:sheet name="30_排他・論理削除" sheetId="31" ns1:id="R8b6542da4c8847e5"/>
+  </ns0:sheets>
+</ns0:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19,7 +19,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="24">
+  <x:fonts count="25">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -154,6 +154,11 @@
       <x:color rgb="FF1F1F1F"/>
       <x:name val="Yu Gothic"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF172B40"/>
+      <x:name val="Yu Gothic"/>
+    </x:font>
   </x:fonts>
   <x:fills count="26">
     <x:fill>
@@ -283,7 +288,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="3">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -299,11 +304,25 @@
         <x:color rgb="FFA6A6A6"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2EC"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2EC"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2EC"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2EC"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="192">
+  <x:cellXfs count="195">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -700,6 +719,15 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1069,7 +1097,7 @@
     <x:row r="11">
       <x:c r="B11"/>
       <x:c r="C11" s="184" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="D11"/>
       <x:c r="E11"/>
@@ -1092,7 +1120,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="D13" s="187" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="E13" s="140"/>
       <x:c r="F13" s="140"/>
@@ -1102,7 +1130,7 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="D14" s="187" t="str">
-        <x:v>2026-09-24</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="E14" s="140"/>
       <x:c r="F14" s="140"/>
@@ -1122,7 +1150,7 @@
         <x:v>状態</x:v>
       </x:c>
       <x:c r="D16" s="187" t="str">
-        <x:v>Review中</x:v>
+        <x:v>修正済</x:v>
       </x:c>
       <x:c r="E16" s="140"/>
       <x:c r="F16" s="140"/>
@@ -1265,7 +1293,7 @@
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
       <x:c r="A4" s="190" t="str">
-        <x:v>版数：Ver.2.5    改訂日：2026-09-24    Baseline：BL-2026-09-24</x:v>
+        <x:v>版数：Ver.2.6    改訂日：2026-09-29    基準Baseline：BL-2026-09-24</x:v>
       </x:c>
       <x:c r="B4" s="63"/>
       <x:c r="C4" s="63"/>
@@ -1611,6 +1639,32 @@
       </x:c>
       <x:c r="H18" s="189" t="str">
         <x:v>BL-2026-09-24。責任者・Review者・承認者はProject Leaderが記入。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="65" customHeight="1">
+      <x:c r="A19" s="194" t="str">
+        <x:v>Ver.2.6</x:v>
+      </x:c>
+      <x:c r="B19" s="194" t="str">
+        <x:v>2026-09-29</x:v>
+      </x:c>
+      <x:c r="C19" s="194" t="str">
+        <x:v>CHG-DB-20260929-01：物理外鍵なしの参照検証・競合防止・関連削除責務を追記。</x:v>
+      </x:c>
+      <x:c r="D19" s="194" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="E19" s="194" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F19" s="194" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="G19" s="194" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="H19" s="194" t="str">
+        <x:v>15／08 DB-REF-001・002参照</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1672,13 +1726,13 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="190" t="str">
-        <x:v>版数：Ver.2.5</x:v>
+        <x:v>版数：Ver.2.6</x:v>
       </x:c>
       <x:c r="B4" s="103"/>
       <x:c r="C4" s="103"/>
       <x:c r="D4" s="105" t="str"/>
       <x:c r="E4" s="63" t="str">
-        <x:v>2026-09-24</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="F4" s="103"/>
       <x:c r="G4" s="103"/>
@@ -2390,13 +2444,13 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="190" t="str">
-        <x:v>版数：Ver.2.5</x:v>
+        <x:v>版数：Ver.2.6</x:v>
       </x:c>
       <x:c r="B4" s="63"/>
       <x:c r="C4" s="63"/>
       <x:c r="D4" s="62" t="str"/>
       <x:c r="E4" s="63" t="str">
-        <x:v>2026-09-24</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="F4" s="63"/>
       <x:c r="G4" s="63"/>
@@ -2743,6 +2797,32 @@
       <x:c r="J18" s="185"/>
       <x:c r="K18" s="185"/>
       <x:c r="L18" s="185"/>
+    </x:row>
+    <x:row r="19" ht="90" customHeight="1">
+      <x:c r="A19" s="194" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B19" s="194" t="str">
+        <x:v>論理参照整合性</x:v>
+      </x:c>
+      <x:c r="C19" s="194" t="str">
+        <x:v>参照IDを登録/変更するAPI・Batch</x:v>
+      </x:c>
+      <x:c r="D19" s="194" t="str">
+        <x:v>同一Transactionで検証</x:v>
+      </x:c>
+      <x:c r="E19" s="194" t="str">
+        <x:v>既定の領域別Lock順で参照先を排他し存在・削除・状態を再確認後に書込。停止/削除側も同じ参照先行を排他して関連行を再確認。</x:v>
+      </x:c>
+      <x:c r="F19" s="194" t="str">
+        <x:v>既存業務Code。失敗時全Rollback。</x:v>
+      </x:c>
+      <x:c r="G19" s="194" t="str">
+        <x:v>既存領域別Lock順を維持。対象組織行のLock順もAPI詳設で固定し、登録側/停止削除側で共有する。</x:v>
+      </x:c>
+      <x:c r="H19" s="194" t="str">
+        <x:v>15／08 DB-REF-001・002</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
